--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 8/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 8/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 12/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 13/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 12/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 13/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 9/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 9/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 14/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 14/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 15/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 15/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 16/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -224,7 +224,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 16/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1550,7 +1550,7 @@
         <v>52</v>
       </c>
       <c r="B7" s="22">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>53</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="121">
   <si>
     <t>Planilla de salario y prestaciones El Salvador 2026</t>
   </si>
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 19/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -164,27 +164,45 @@
     <t>Indemnización por despido y prestación por renuncia</t>
   </si>
   <si>
+    <t>Comercio y servicios</t>
+  </si>
+  <si>
+    <t>Industria (incluye ingenios azucareros y agroindustria)</t>
+  </si>
+  <si>
+    <t>Maquila textil y confección</t>
+  </si>
+  <si>
     <t>Años de servicio</t>
   </si>
   <si>
+    <t>Beneficios de café</t>
+  </si>
+  <si>
     <t>Días después del último aniversario</t>
   </si>
   <si>
+    <t>Recolección de caña de azúcar</t>
+  </si>
+  <si>
     <t>Fecha en que empezó a trabajar</t>
   </si>
   <si>
+    <t>Agropecuario, pesca y otras actividades agrícolas</t>
+  </si>
+  <si>
     <t>Último día trabajado</t>
   </si>
   <si>
     <t>Salario mínimo diario del sector</t>
   </si>
   <si>
+    <t>Recolección de café</t>
+  </si>
+  <si>
     <t>Sector de la empresa</t>
   </si>
   <si>
-    <t>Comercio y servicios</t>
-  </si>
-  <si>
     <t>Indemnización</t>
   </si>
   <si>
@@ -224,7 +242,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 19/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -330,24 +348,6 @@
   </si>
   <si>
     <t>https://www.jurisprudencia.gob.sv/DocumentosBoveda/D/2/2020-2029/2025/05/10A4DA.PDF</t>
-  </si>
-  <si>
-    <t>Industria (incluye ingenios azucareros y agroindustria)</t>
-  </si>
-  <si>
-    <t>Maquila textil y confección</t>
-  </si>
-  <si>
-    <t>Beneficios de café</t>
-  </si>
-  <si>
-    <t>Recolección de caña de azúcar</t>
-  </si>
-  <si>
-    <t>Agropecuario, pesca y otras actividades agrícolas</t>
-  </si>
-  <si>
-    <t>Recolección de café</t>
   </si>
   <si>
     <t>Tope del salario diario para la indemnización (veces el salario mínimo diario)</t>
@@ -1477,7 +1477,7 @@
   <sheetPr>
     <tabColor rgb="FF1B5E20"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -1486,35 +1486,50 @@
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
-    </row>
-    <row r="3" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="26:26" x14ac:dyDescent="0.25">
+      <c r="Z2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="5:26" x14ac:dyDescent="0.25">
       <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
       <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
       <c r="E4" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F4" s="13">
         <f>IF(EDATE(B6,12*(YEAR((B7+1))-YEAR(B6)))&gt;(B7+1),(YEAR((B7+1))-YEAR(B6))-1,(YEAR((B7+1))-YEAR(B6)))</f>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>30</v>
       </c>
@@ -1525,15 +1540,18 @@
         <v>31</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F5" s="13">
         <f>(B7+1)-EDATE(B6,12*F4)</f>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B6" s="22">
         <v>44228</v>
@@ -1544,42 +1562,48 @@
       <c r="F6" s="8">
         <f>B5/30</f>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="Z6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B7" s="22">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F7" s="8">
         <f>INDEX('Tablas oficiales'!$C$24:$C$30,MATCH(B8,'Tablas oficiales'!$B$24:$B$30,0))</f>
       </c>
+      <c r="Z7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E9" s="23" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="E10" s="7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F10" s="8">
         <f>MIN(F6,'Tablas oficiales'!$C$31*F7)</f>
@@ -1592,7 +1616,7 @@
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
       <c r="E11" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F11" s="20">
         <f>MAX('Tablas oficiales'!$C$32*F4+'Tablas oficiales'!$C$32*F5/365,'Tablas oficiales'!$C$33)</f>
@@ -1600,7 +1624,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B12" s="24">
         <f>F4&amp;" años y "&amp;F5&amp;" días"</f>
@@ -1608,24 +1632,24 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B13" s="16">
         <f>ROUND(F10,2)</f>
       </c>
       <c r="E13" s="23" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B14" s="21">
         <f>ROUND(F11,2)</f>
       </c>
       <c r="E14" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F14" s="8">
         <f>MIN(F6,'Tablas oficiales'!$C$34*F7)</f>
@@ -1633,13 +1657,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B15" s="18">
         <f>ROUND(F10*F11,2)</f>
       </c>
       <c r="E15" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F15" s="13">
         <f>IF(F4&gt;='Tablas oficiales'!$C$35,'Tablas oficiales'!$C$36*F4,0)</f>
@@ -1647,21 +1671,21 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B20" s="16">
         <f>ROUND(F14,2)</f>
@@ -1669,7 +1693,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B21" s="25">
         <f>F15</f>
@@ -1677,7 +1701,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B22" s="18">
         <f>ROUND(F14*F15,2)</f>
@@ -1685,7 +1709,7 @@
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1709,8 +1733,8 @@
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Escribe una fecha como dd/mm/aaaa." sqref="B6:B7">
       <formula1>18264</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista." sqref="B8">
-      <formula1>'Tablas oficiales'!$B$24:$B$30</formula1>
+    <dataValidation type="list" showErrorMessage="1" error="Elige una opción de la lista (Sector de la empresa)." sqref="B8">
+      <formula1>'Indemnización y renuncia'!$Z$1:$Z$7</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1737,7 +1761,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -1748,7 +1772,7 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1759,81 +1783,81 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C4" s="29">
         <v>7.25</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="34" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -1894,35 +1918,35 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
@@ -1983,7 +2007,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B19" s="38" t="s">
         <v>39</v>
@@ -1992,269 +2016,269 @@
         <v>15</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F19" s="40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C20" s="29">
         <v>19</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C21" s="39">
         <v>21</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C22" s="41">
         <v>1500</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C23" s="39">
         <v>50</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F23" s="40" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C24" s="41">
         <v>13.44</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="C25" s="42">
         <v>13.44</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E25" s="38" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="C26" s="41">
         <v>13.227</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C27" s="42">
         <v>10.035</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C28" s="41">
         <v>10.035</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="C29" s="42">
         <v>8.96</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C30" s="41">
         <v>8.96</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2262,7 +2286,7 @@
         <v>111</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C31" s="39">
         <v>4</v>
@@ -2271,13 +2295,13 @@
         <v>112</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2285,22 +2309,22 @@
         <v>113</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C32" s="29">
         <v>30</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2308,22 +2332,22 @@
         <v>114</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C33" s="39">
         <v>15</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F33" s="40" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2331,7 +2355,7 @@
         <v>115</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C34" s="29">
         <v>2</v>
@@ -2346,7 +2370,7 @@
         <v>117</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2354,7 +2378,7 @@
         <v>118</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C35" s="39">
         <v>2</v>
@@ -2369,7 +2393,7 @@
         <v>117</v>
       </c>
       <c r="G35" s="38" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2377,13 +2401,13 @@
         <v>120</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C36" s="29">
         <v>15</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E36" s="28" t="s">
         <v>116</v>
@@ -2392,7 +2416,7 @@
         <v>117</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 20/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -242,7 +242,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 20/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1571,7 +1571,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="22">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>59</v>

--- a/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
+++ b/private/intl/sv/sueldo-y-liquidacion-2026.xlsx
@@ -32,7 +32,7 @@
     <t>«Indemnización y renuncia»: pone sus fechas y su salario, y le dice la indemnización por despido sin causa o la prestación por renuncia voluntaria.</t>
   </si>
   <si>
-    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 21/10/2026.</t>
+    <t>«Tablas oficiales» tiene cada valor oficial que usan las fórmulas, con el enlace a su fuente y la fecha en que lo verificamos. Los valores son los vigentes al 22/10/2026.</t>
   </si>
   <si>
     <t>Cuando cambia un valor oficial, actualizamos la planilla y el mismo enlace de descarga le baja la versión nueva.</t>
@@ -242,7 +242,7 @@
     <t>Tablas oficiales de El Salvador</t>
   </si>
   <si>
-    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 21/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
+    <t>Son los valores que usan las fórmulas de esta planilla, vigentes al 22/10/2026. Cada uno trae el enlace a la norma o al organismo que lo publica y la fecha en que lo verificamos.</t>
   </si>
   <si>
     <t>Dato</t>
@@ -1571,7 +1571,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="22">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>59</v>
